--- a/data/trans_orig/IP31KM14_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM14_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6250</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3070</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12332</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10,37%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20,46%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4869</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1588</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12564</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,82%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7740</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>6785</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12609</t>
+          <t>9364</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22301</t>
+          <t>14769</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>54013</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47931</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>57193</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>89,63%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>79,54%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,91%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>66531</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>58836</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>69812</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>93,18%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>82,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66867</t>
+          <t>51808</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60964</t>
+          <t>48137</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70803</t>
+          <t>53791</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>133398</t>
+          <t>105822</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>123706</t>
+          <t>100417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>138941</t>
+          <t>109877</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17548</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11111</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25878</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15,27%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,67%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,51%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10014</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3970</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17038</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,56%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19226</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12090</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27632</t>
+          <t>15824</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>29240</t>
+          <t>27153</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17740</t>
+          <t>19290</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40323</t>
+          <t>37399</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>97403</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>89073</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>103840</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77,49%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,33%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>115635</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>108611</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>121679</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>92,03%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,44%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>107197</t>
+          <t>89728</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>98791</t>
+          <t>83509</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>114333</t>
+          <t>93689</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>222831</t>
+          <t>187131</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>211748</t>
+          <t>176885</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>234331</t>
+          <t>194994</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8039</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4766</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12923</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14,03%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9210</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5838</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14569</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16,58%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9508</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>14144</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>18718</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13190</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26294</t>
+          <t>24224</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>49260</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>44376</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>52533</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>85,97%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,68%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>46342</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>40983</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>49714</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>83,42%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>73,77%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,49%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>55125</t>
+          <t>44890</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49467</t>
+          <t>39968</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59131</t>
+          <t>48604</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>101467</t>
+          <t>94150</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>93891</t>
+          <t>87187</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>106995</t>
+          <t>99510</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,32%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18566</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10075</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>28706</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26,59%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>41,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>14370</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8678</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20436</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>20,62%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,45%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,33%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18699</t>
+          <t>14647</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10126</t>
+          <t>9538</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29007</t>
+          <t>22074</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>33069</t>
+          <t>33213</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21890</t>
+          <t>23394</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44540</t>
+          <t>45106</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>51250</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>41110</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>59741</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>73,41%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>58,88%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>55312</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>49246</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>61004</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>79,38%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>70,67%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,55%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>56668</t>
+          <t>55815</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46360</t>
+          <t>48388</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65241</t>
+          <t>60924</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>111980</t>
+          <t>107065</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>100509</t>
+          <t>95172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>123159</t>
+          <t>116884</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>83,32%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3833</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1659</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7329</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,69%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1095</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3671</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3365</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,73%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3798</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1509</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7122</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,33%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8824</t>
+          <t>8479</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -2205,74 +2205,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>35746</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>32250</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>37920</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,31%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>33105</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>30529</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>96,8%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,27%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>34331</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>32005</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>35370</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>97,06%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>90,49%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>36921</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>33597</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>39210</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>90,67%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>82,51%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>96,29%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>129</t>
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>70026</t>
+          <t>70076</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66095</t>
+          <t>66470</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72644</t>
+          <t>72688</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11191</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6495</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11029</t>
+          <t>11262</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>13278</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>41230</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>36220</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>43912</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>87,34%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>76,72%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>93,02%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>37508</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>33099</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>40586</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>84,69%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>74,73%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>91,64%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>47287</t>
+          <t>37530</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42753</t>
+          <t>33024</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50778</t>
+          <t>40721</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>84794</t>
+          <t>78760</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78953</t>
+          <t>72697</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>89605</t>
+          <t>83075</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>49431</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>39760</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>61408</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>35,16%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>28,28%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>43,68%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>43198</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>34221</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>54443</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>34,92%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>27,67%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>44,01%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>57377</t>
+          <t>41070</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46641</t>
+          <t>32298</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73446</t>
+          <t>49850</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>100575</t>
+          <t>90501</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86088</t>
+          <t>75995</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119626</t>
+          <t>104664</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>39,89%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>91140</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>79163</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>100811</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>64,84%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>56,32%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>71,72%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>80498</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>69253</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>89475</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>65,08%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>55,99%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>72,33%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>97667</t>
+          <t>80752</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>81598</t>
+          <t>71972</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>108403</t>
+          <t>89524</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>178165</t>
+          <t>171893</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>159114</t>
+          <t>157730</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>192652</t>
+          <t>186399</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>71,04%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>18208</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>11848</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>25212</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>11,59%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>7,54%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>16,04%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>24642</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>17918</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>34221</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>19,15%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>13,93%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>26,6%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>26742</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12517</t>
+          <t>19036</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>37890</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>43009</t>
+          <t>44951</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32453</t>
+          <t>34524</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53623</t>
+          <t>57288</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>138928</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>131924</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>145288</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>88,41%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>83,96%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>92,46%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>104023</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>94444</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>110747</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>80,85%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>73,4%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>86,07%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>135792</t>
+          <t>111158</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>127516</t>
+          <t>100010</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>141642</t>
+          <t>118864</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>239814</t>
+          <t>250085</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>229200</t>
+          <t>237748</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>250370</t>
+          <t>260512</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,3%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>127855</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>110698</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>148862</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>18,62%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>21,67%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>114180</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>94435</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>134058</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>17,48%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>14,46%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>20,53%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>141210</t>
+          <t>112195</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>120956</t>
+          <t>95356</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>168997</t>
+          <t>129370</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>255390</t>
+          <t>240050</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>226784</t>
+          <t>215056</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>288156</t>
+          <t>265890</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>773</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>558969</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>537962</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>576126</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>81,38%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>78,33%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>83,88%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>758</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>538954</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>519076</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>558699</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>82,52%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>79,47%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>85,54%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>773</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>603523</t>
+          <t>506013</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>575736</t>
+          <t>488838</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>623777</t>
+          <t>522852</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1142477</t>
+          <t>1064981</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1109711</t>
+          <t>1039141</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1171083</t>
+          <t>1089975</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,52%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
